--- a/avanceSEGMA.xlsx
+++ b/avanceSEGMA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
-  <workbookPr showInkAnnotation="0" defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30502"/>
+  <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alvar\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avitaconstructora-my.sharepoint.com/personal/aolivares_avita_cl/Documents/OT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D5DF81D-3ABD-4774-BCE1-0C56C7604FD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="127" documentId="7_{30C0E4BA-C577-AA4F-9580-3F64A608DEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0E3805F-3024-4F5D-914A-439E67E81C2A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="6">
   <si>
     <t>partida</t>
   </si>
@@ -63,7 +63,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -440,14 +440,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9976E081-C2DF-2D4C-9457-A38B86FA81C8}">
-  <dimension ref="A1:C28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -458,7 +458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -470,7 +470,7 @@
         <v>28.333333333333332</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -479,7 +479,7 @@
       </c>
       <c r="C3" s="4"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -488,7 +488,7 @@
       </c>
       <c r="C4" s="4"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -500,7 +500,7 @@
         <v>32.666666666666664</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -511,7 +511,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -520,7 +520,7 @@
       </c>
       <c r="C7" s="3"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -531,7 +531,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -542,7 +542,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -551,7 +551,7 @@
       </c>
       <c r="C10" s="3"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -562,7 +562,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -573,7 +573,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -582,7 +582,7 @@
       </c>
       <c r="C13" s="3"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -593,7 +593,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -604,7 +604,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -613,7 +613,7 @@
       </c>
       <c r="C16" s="3"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -624,7 +624,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -635,7 +635,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -644,7 +644,7 @@
       </c>
       <c r="C19" s="3"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -655,7 +655,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -666,7 +666,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -675,7 +675,7 @@
       </c>
       <c r="C22" s="3"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -686,7 +686,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -697,7 +697,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -708,7 +708,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -719,7 +719,7 @@
         <v>72.709999999999994</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -730,7 +730,7 @@
         <v>38.75</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>5</v>
       </c>
@@ -741,9 +741,42 @@
         <v>33</v>
       </c>
     </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29" s="1">
+        <v>46276</v>
+      </c>
+      <c r="C29">
+        <v>89.6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="1">
+        <v>46276</v>
+      </c>
+      <c r="C30">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31" s="1">
+        <v>46276</v>
+      </c>
+      <c r="C31">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A29:A37" xr:uid="{26D849AA-A1E8-4BB2-8DD5-D8AFA8E1214D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A32:A37" xr:uid="{26D849AA-A1E8-4BB2-8DD5-D8AFA8E1214D}">
       <formula1>$A$2:$A$4</formula1>
     </dataValidation>
   </dataValidations>

--- a/avanceSEGMA.xlsx
+++ b/avanceSEGMA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avitaconstructora-my.sharepoint.com/personal/aolivares_avita_cl/Documents/OT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="127" documentId="7_{30C0E4BA-C577-AA4F-9580-3F64A608DEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0E3805F-3024-4F5D-914A-439E67E81C2A}"/>
+  <xr:revisionPtr revIDLastSave="134" documentId="7_{30C0E4BA-C577-AA4F-9580-3F64A608DEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3454385A-4E70-46C1-82FB-2B96B55C09FA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="6">
   <si>
     <t>partida</t>
   </si>
@@ -440,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9976E081-C2DF-2D4C-9457-A38B86FA81C8}">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
@@ -774,9 +774,42 @@
         <v>33</v>
       </c>
     </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B32" s="1">
+        <v>46280</v>
+      </c>
+      <c r="C32">
+        <v>91.34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" s="1">
+        <v>46280</v>
+      </c>
+      <c r="C33">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" s="1">
+        <v>46280</v>
+      </c>
+      <c r="C34">
+        <v>58.08</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A32:A37" xr:uid="{26D849AA-A1E8-4BB2-8DD5-D8AFA8E1214D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A35:A37" xr:uid="{26D849AA-A1E8-4BB2-8DD5-D8AFA8E1214D}">
       <formula1>$A$2:$A$4</formula1>
     </dataValidation>
   </dataValidations>

--- a/avanceSEGMA.xlsx
+++ b/avanceSEGMA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avitaconstructora-my.sharepoint.com/personal/aolivares_avita_cl/Documents/OT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="134" documentId="7_{30C0E4BA-C577-AA4F-9580-3F64A608DEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3454385A-4E70-46C1-82FB-2B96B55C09FA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1CB86EB5-E018-4874-8C07-4D6686A8E3BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="6">
   <si>
     <t>partida</t>
   </si>
@@ -440,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9976E081-C2DF-2D4C-9457-A38B86FA81C8}">
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
@@ -807,12 +807,40 @@
         <v>58.08</v>
       </c>
     </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>3</v>
+      </c>
+      <c r="B35" s="1">
+        <v>46281</v>
+      </c>
+      <c r="C35">
+        <v>93.38</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="1">
+        <v>46281</v>
+      </c>
+      <c r="C36">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>5</v>
+      </c>
+      <c r="B37" s="1">
+        <v>46281</v>
+      </c>
+      <c r="C37">
+        <v>58.08</v>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A35:A37" xr:uid="{26D849AA-A1E8-4BB2-8DD5-D8AFA8E1214D}">
-      <formula1>$A$2:$A$4</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="14" scale="130" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/avanceSEGMA.xlsx
+++ b/avanceSEGMA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30502"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avitaconstructora-my.sharepoint.com/personal/aolivares_avita_cl/Documents/OT/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avitaconstructora-my.sharepoint.com/personal/aolivares_avita_cl/Documents/OT/netlify-drop-segma/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1CB86EB5-E018-4874-8C07-4D6686A8E3BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{38193824-6CBE-498C-BB1B-1CCBB30AFBB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="6">
   <si>
     <t>partida</t>
   </si>
@@ -440,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9976E081-C2DF-2D4C-9457-A38B86FA81C8}">
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
@@ -705,7 +705,7 @@
         <v>46260</v>
       </c>
       <c r="C25" s="3">
-        <v>33</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -713,10 +713,10 @@
         <v>3</v>
       </c>
       <c r="B26" s="1">
-        <v>46267</v>
-      </c>
-      <c r="C26" s="3">
-        <v>72.709999999999994</v>
+        <v>46261</v>
+      </c>
+      <c r="C26">
+        <v>65.400000000000006</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -724,10 +724,10 @@
         <v>4</v>
       </c>
       <c r="B27" s="1">
-        <v>46267</v>
-      </c>
-      <c r="C27" s="3">
-        <v>38.75</v>
+        <v>46261</v>
+      </c>
+      <c r="C27">
+        <v>60.6</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -735,10 +735,10 @@
         <v>5</v>
       </c>
       <c r="B28" s="1">
-        <v>46267</v>
-      </c>
-      <c r="C28" s="3">
-        <v>33</v>
+        <v>46261</v>
+      </c>
+      <c r="C28">
+        <v>34.1</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -746,10 +746,10 @@
         <v>3</v>
       </c>
       <c r="B29" s="1">
-        <v>46276</v>
-      </c>
-      <c r="C29">
-        <v>89.6</v>
+        <v>46260</v>
+      </c>
+      <c r="C29" s="3">
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -757,10 +757,10 @@
         <v>4</v>
       </c>
       <c r="B30" s="1">
-        <v>46276</v>
-      </c>
-      <c r="C30">
-        <v>39.5</v>
+        <v>46260</v>
+      </c>
+      <c r="C30" s="3">
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -768,9 +768,9 @@
         <v>5</v>
       </c>
       <c r="B31" s="1">
-        <v>46276</v>
-      </c>
-      <c r="C31">
+        <v>46260</v>
+      </c>
+      <c r="C31" s="3">
         <v>33</v>
       </c>
     </row>
@@ -779,10 +779,10 @@
         <v>3</v>
       </c>
       <c r="B32" s="1">
-        <v>46280</v>
-      </c>
-      <c r="C32">
-        <v>91.34</v>
+        <v>46267</v>
+      </c>
+      <c r="C32" s="3">
+        <v>72.709999999999994</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -790,10 +790,10 @@
         <v>4</v>
       </c>
       <c r="B33" s="1">
-        <v>46280</v>
-      </c>
-      <c r="C33">
-        <v>40.5</v>
+        <v>46267</v>
+      </c>
+      <c r="C33" s="3">
+        <v>38.75</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -801,10 +801,10 @@
         <v>5</v>
       </c>
       <c r="B34" s="1">
-        <v>46280</v>
-      </c>
-      <c r="C34">
-        <v>58.08</v>
+        <v>46267</v>
+      </c>
+      <c r="C34" s="3">
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -812,10 +812,10 @@
         <v>3</v>
       </c>
       <c r="B35" s="1">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="C35">
-        <v>93.38</v>
+        <v>89.6</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -823,10 +823,10 @@
         <v>4</v>
       </c>
       <c r="B36" s="1">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="C36">
-        <v>41</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -834,13 +834,117 @@
         <v>5</v>
       </c>
       <c r="B37" s="1">
+        <v>46276</v>
+      </c>
+      <c r="C37">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>3</v>
+      </c>
+      <c r="B38" s="1">
+        <v>46280</v>
+      </c>
+      <c r="C38">
+        <v>91.34</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" s="1">
+        <v>46280</v>
+      </c>
+      <c r="C39">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40" s="1">
+        <v>46280</v>
+      </c>
+      <c r="C40">
+        <v>58.08</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>3</v>
+      </c>
+      <c r="B41" s="1">
         <v>46281</v>
       </c>
-      <c r="C37">
+      <c r="C41">
+        <v>93.38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="1">
+        <v>46281</v>
+      </c>
+      <c r="C42">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43" s="1">
+        <v>46281</v>
+      </c>
+      <c r="C43">
         <v>58.08</v>
       </c>
     </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B44" s="1">
+        <v>46277</v>
+      </c>
+      <c r="C44">
+        <v>93.59</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" s="1">
+        <v>46277</v>
+      </c>
+      <c r="C45">
+        <v>42.72</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>5</v>
+      </c>
+      <c r="B46" s="1">
+        <v>46277</v>
+      </c>
+      <c r="C46">
+        <v>58.08</v>
+      </c>
+    </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A29:A37" xr:uid="{26D849AA-A1E8-4BB2-8DD5-D8AFA8E1214D}">
+      <formula1>$A$2:$A$4</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="14" scale="130" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/avanceSEGMA.xlsx
+++ b/avanceSEGMA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avitaconstructora-my.sharepoint.com/personal/aolivares_avita_cl/Documents/OT/netlify-drop-segma/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{38193824-6CBE-498C-BB1B-1CCBB30AFBB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E9CBB0E-25CE-4711-B833-1AE6C2EBD2E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -911,7 +911,7 @@
         <v>3</v>
       </c>
       <c r="B44" s="1">
-        <v>46277</v>
+        <v>46288</v>
       </c>
       <c r="C44">
         <v>93.59</v>
@@ -922,7 +922,7 @@
         <v>4</v>
       </c>
       <c r="B45" s="1">
-        <v>46277</v>
+        <v>46288</v>
       </c>
       <c r="C45">
         <v>42.72</v>
@@ -933,7 +933,7 @@
         <v>5</v>
       </c>
       <c r="B46" s="1">
-        <v>46277</v>
+        <v>46288</v>
       </c>
       <c r="C46">
         <v>58.08</v>

--- a/avanceSEGMA.xlsx
+++ b/avanceSEGMA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avitaconstructora-my.sharepoint.com/personal/aolivares_avita_cl/Documents/OT/netlify-drop-segma/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E9CBB0E-25CE-4711-B833-1AE6C2EBD2E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F63A8F1-130C-41EC-A35C-33766630F391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -727,7 +727,7 @@
         <v>46261</v>
       </c>
       <c r="C27">
-        <v>60.6</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -771,7 +771,7 @@
         <v>46260</v>
       </c>
       <c r="C31" s="3">
-        <v>33</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -804,7 +804,7 @@
         <v>46267</v>
       </c>
       <c r="C34" s="3">
-        <v>33</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -837,7 +837,7 @@
         <v>46276</v>
       </c>
       <c r="C37">
-        <v>33</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="38" spans="1:3">

--- a/avanceSEGMA.xlsx
+++ b/avanceSEGMA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
-  <workbookPr showInkAnnotation="0"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30515"/>
+  <workbookPr showInkAnnotation="0" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avitaconstructora-my.sharepoint.com/personal/aolivares_avita_cl/Documents/OT/netlify-drop-segma/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F63A8F1-130C-41EC-A35C-33766630F391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="145" documentId="7_{30C0E4BA-C577-AA4F-9580-3F64A608DEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBE5484F-943C-4AC1-90FD-7307403E8C53}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -441,13 +441,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9976E081-C2DF-2D4C-9457-A38B86FA81C8}">
   <dimension ref="A1:C46"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -458,7 +458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -470,7 +470,7 @@
         <v>28.333333333333332</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -479,7 +479,7 @@
       </c>
       <c r="C3" s="4"/>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -488,7 +488,7 @@
       </c>
       <c r="C4" s="4"/>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -500,7 +500,7 @@
         <v>32.666666666666664</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -511,7 +511,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -520,7 +520,7 @@
       </c>
       <c r="C7" s="3"/>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -531,7 +531,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -542,7 +542,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -551,7 +551,7 @@
       </c>
       <c r="C10" s="3"/>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -562,7 +562,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -573,7 +573,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -582,7 +582,7 @@
       </c>
       <c r="C13" s="3"/>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -593,7 +593,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -604,7 +604,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -613,7 +613,7 @@
       </c>
       <c r="C16" s="3"/>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -624,7 +624,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -635,7 +635,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -644,7 +644,7 @@
       </c>
       <c r="C19" s="3"/>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -655,7 +655,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -666,7 +666,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -675,7 +675,7 @@
       </c>
       <c r="C22" s="3"/>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -686,7 +686,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -697,7 +697,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -708,7 +708,7 @@
         <v>34.1</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -719,7 +719,7 @@
         <v>65.400000000000006</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -730,7 +730,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>5</v>
       </c>
@@ -741,7 +741,7 @@
         <v>34.1</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>3</v>
       </c>
@@ -749,10 +749,10 @@
         <v>46260</v>
       </c>
       <c r="C29" s="3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
+        <v>68.33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -763,7 +763,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -774,7 +774,7 @@
         <v>34.1</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>3</v>
       </c>
@@ -785,7 +785,7 @@
         <v>72.709999999999994</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>4</v>
       </c>
@@ -796,7 +796,7 @@
         <v>38.75</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -807,7 +807,7 @@
         <v>34.1</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>3</v>
       </c>
@@ -818,7 +818,7 @@
         <v>89.6</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>4</v>
       </c>
@@ -829,7 +829,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -840,7 +840,7 @@
         <v>34.1</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>3</v>
       </c>
@@ -851,7 +851,7 @@
         <v>91.34</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>4</v>
       </c>
@@ -862,7 +862,7 @@
         <v>40.5</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>5</v>
       </c>
@@ -873,7 +873,7 @@
         <v>58.08</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>3</v>
       </c>
@@ -884,7 +884,7 @@
         <v>93.38</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>4</v>
       </c>
@@ -895,7 +895,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>5</v>
       </c>
@@ -906,7 +906,7 @@
         <v>58.08</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>3</v>
       </c>
@@ -914,10 +914,10 @@
         <v>46288</v>
       </c>
       <c r="C44">
-        <v>93.59</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
+        <v>94.22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>4</v>
       </c>
@@ -928,7 +928,7 @@
         <v>42.72</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>5</v>
       </c>

--- a/avanceSEGMA.xlsx
+++ b/avanceSEGMA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avitaconstructora-my.sharepoint.com/personal/aolivares_avita_cl/Documents/OT/netlify-drop-segma/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="145" documentId="7_{30C0E4BA-C577-AA4F-9580-3F64A608DEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBE5484F-943C-4AC1-90FD-7307403E8C53}"/>
+  <xr:revisionPtr revIDLastSave="148" documentId="7_{30C0E4BA-C577-AA4F-9580-3F64A608DEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E83D1E1-6F77-4FF4-BCC7-4BE0E2D09254}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -746,7 +746,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="1">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="C29" s="3">
         <v>68.33</v>
@@ -757,7 +757,7 @@
         <v>4</v>
       </c>
       <c r="B30" s="1">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="C30" s="3">
         <v>35</v>
@@ -768,7 +768,7 @@
         <v>5</v>
       </c>
       <c r="B31" s="1">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="C31" s="3">
         <v>34.1</v>

--- a/avanceSEGMA.xlsx
+++ b/avanceSEGMA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30515"/>
-  <workbookPr showInkAnnotation="0" defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30524"/>
+  <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avitaconstructora-my.sharepoint.com/personal/aolivares_avita_cl/Documents/OT/netlify-drop-segma/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avitaconstructora-my.sharepoint.com/personal/aolivares_avita_cl/Documents/OT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="148" documentId="7_{30C0E4BA-C577-AA4F-9580-3F64A608DEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E83D1E1-6F77-4FF4-BCC7-4BE0E2D09254}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6996F7D7-92A5-484A-AC4D-4485DF1482F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="6">
   <si>
     <t>partida</t>
   </si>
@@ -63,7 +63,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -440,14 +440,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9976E081-C2DF-2D4C-9457-A38B86FA81C8}">
-  <dimension ref="A1:C46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C40"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -458,7 +458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -470,7 +470,7 @@
         <v>28.333333333333332</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -479,7 +479,7 @@
       </c>
       <c r="C3" s="4"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -488,7 +488,7 @@
       </c>
       <c r="C4" s="4"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -500,7 +500,7 @@
         <v>32.666666666666664</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -511,7 +511,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -520,7 +520,7 @@
       </c>
       <c r="C7" s="3"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -531,7 +531,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -542,7 +542,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -551,7 +551,7 @@
       </c>
       <c r="C10" s="3"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -562,7 +562,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -573,7 +573,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -582,7 +582,7 @@
       </c>
       <c r="C13" s="3"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -593,7 +593,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -604,7 +604,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -613,7 +613,7 @@
       </c>
       <c r="C16" s="3"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -624,7 +624,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -635,7 +635,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -644,7 +644,7 @@
       </c>
       <c r="C19" s="3"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -655,7 +655,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -666,7 +666,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -675,7 +675,7 @@
       </c>
       <c r="C22" s="3"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -686,7 +686,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -697,7 +697,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -705,246 +705,175 @@
         <v>46260</v>
       </c>
       <c r="C25" s="3">
-        <v>34.1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>3</v>
       </c>
       <c r="B26" s="1">
-        <v>46261</v>
-      </c>
-      <c r="C26">
-        <v>65.400000000000006</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46267</v>
+      </c>
+      <c r="C26" s="3">
+        <v>72.709999999999994</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>4</v>
       </c>
       <c r="B27" s="1">
-        <v>46261</v>
-      </c>
-      <c r="C27">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46267</v>
+      </c>
+      <c r="C27" s="3">
+        <v>38.75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>5</v>
       </c>
       <c r="B28" s="1">
-        <v>46261</v>
-      </c>
-      <c r="C28">
-        <v>34.1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46267</v>
+      </c>
+      <c r="C28" s="3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>3</v>
       </c>
       <c r="B29" s="1">
-        <v>46265</v>
-      </c>
-      <c r="C29" s="3">
-        <v>68.33</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46276</v>
+      </c>
+      <c r="C29">
+        <v>89.6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>4</v>
       </c>
       <c r="B30" s="1">
-        <v>46265</v>
-      </c>
-      <c r="C30" s="3">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46276</v>
+      </c>
+      <c r="C30">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>5</v>
       </c>
       <c r="B31" s="1">
-        <v>46265</v>
-      </c>
-      <c r="C31" s="3">
-        <v>34.1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46276</v>
+      </c>
+      <c r="C31">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>3</v>
       </c>
       <c r="B32" s="1">
-        <v>46267</v>
-      </c>
-      <c r="C32" s="3">
-        <v>72.709999999999994</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46280</v>
+      </c>
+      <c r="C32">
+        <v>91.34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>4</v>
       </c>
       <c r="B33" s="1">
-        <v>46267</v>
-      </c>
-      <c r="C33" s="3">
-        <v>38.75</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46280</v>
+      </c>
+      <c r="C33">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>5</v>
       </c>
       <c r="B34" s="1">
-        <v>46267</v>
-      </c>
-      <c r="C34" s="3">
-        <v>34.1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46280</v>
+      </c>
+      <c r="C34">
+        <v>58.08</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>3</v>
       </c>
       <c r="B35" s="1">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="C35">
-        <v>89.6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+        <v>93.38</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>4</v>
       </c>
       <c r="B36" s="1">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="C36">
-        <v>39.5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>5</v>
       </c>
       <c r="B37" s="1">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="C37">
-        <v>34.1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+        <v>58.08</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>3</v>
       </c>
       <c r="B38" s="1">
-        <v>46280</v>
+        <v>46293</v>
       </c>
       <c r="C38">
-        <v>91.34</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+        <v>96.25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>4</v>
       </c>
       <c r="B39" s="1">
-        <v>46280</v>
+        <v>46293</v>
       </c>
       <c r="C39">
-        <v>40.5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+        <v>63.07</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
         <v>5</v>
       </c>
       <c r="B40" s="1">
-        <v>46280</v>
+        <v>46293</v>
       </c>
       <c r="C40">
-        <v>58.08</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>3</v>
-      </c>
-      <c r="B41" s="1">
-        <v>46281</v>
-      </c>
-      <c r="C41">
-        <v>93.38</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>4</v>
-      </c>
-      <c r="B42" s="1">
-        <v>46281</v>
-      </c>
-      <c r="C42">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>5</v>
-      </c>
-      <c r="B43" s="1">
-        <v>46281</v>
-      </c>
-      <c r="C43">
-        <v>58.08</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>3</v>
-      </c>
-      <c r="B44" s="1">
-        <v>46288</v>
-      </c>
-      <c r="C44">
-        <v>94.22</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>4</v>
-      </c>
-      <c r="B45" s="1">
-        <v>46288</v>
-      </c>
-      <c r="C45">
-        <v>42.72</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>5</v>
-      </c>
-      <c r="B46" s="1">
-        <v>46288</v>
-      </c>
-      <c r="C46">
-        <v>58.08</v>
+        <v>67.099999999999994</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A29:A37" xr:uid="{26D849AA-A1E8-4BB2-8DD5-D8AFA8E1214D}">
-      <formula1>$A$2:$A$4</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="14" scale="130" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/avanceSEGMA.xlsx
+++ b/avanceSEGMA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30524"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30602"/>
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avitaconstructora-my.sharepoint.com/personal/aolivares_avita_cl/Documents/OT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6996F7D7-92A5-484A-AC4D-4485DF1482F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F87FAF16-CB8F-4BF1-94CB-32D2AB8D8A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="6">
   <si>
     <t>partida</t>
   </si>
@@ -440,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9976E081-C2DF-2D4C-9457-A38B86FA81C8}">
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
@@ -873,6 +873,39 @@
         <v>67.099999999999994</v>
       </c>
     </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>3</v>
+      </c>
+      <c r="B41" s="1">
+        <v>46300</v>
+      </c>
+      <c r="C41">
+        <v>97.48</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="1">
+        <v>46300</v>
+      </c>
+      <c r="C42">
+        <v>69.459999999999994</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43" s="1">
+        <v>46300</v>
+      </c>
+      <c r="C43">
+        <v>74.73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="14" scale="130" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/avanceSEGMA.xlsx
+++ b/avanceSEGMA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30602"/>
-  <workbookPr showInkAnnotation="0"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30601"/>
+  <workbookPr showInkAnnotation="0" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avitaconstructora-my.sharepoint.com/personal/aolivares_avita_cl/Documents/OT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F87FAF16-CB8F-4BF1-94CB-32D2AB8D8A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="159" documentId="7_{30C0E4BA-C577-AA4F-9580-3F64A608DEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A94F71CC-4A71-44A2-BA0D-AB1150F48CF9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -441,13 +441,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9976E081-C2DF-2D4C-9457-A38B86FA81C8}">
   <dimension ref="A1:C43"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -458,7 +458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -470,7 +470,7 @@
         <v>28.333333333333332</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -479,7 +479,7 @@
       </c>
       <c r="C3" s="4"/>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -488,7 +488,7 @@
       </c>
       <c r="C4" s="4"/>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -500,7 +500,7 @@
         <v>32.666666666666664</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -511,7 +511,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -520,7 +520,7 @@
       </c>
       <c r="C7" s="3"/>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -531,7 +531,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -542,7 +542,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -551,7 +551,7 @@
       </c>
       <c r="C10" s="3"/>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -562,7 +562,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -573,7 +573,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -582,7 +582,7 @@
       </c>
       <c r="C13" s="3"/>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -593,7 +593,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -604,7 +604,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -613,7 +613,7 @@
       </c>
       <c r="C16" s="3"/>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -624,7 +624,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -635,7 +635,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -644,7 +644,7 @@
       </c>
       <c r="C19" s="3"/>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -655,7 +655,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -666,7 +666,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -675,7 +675,7 @@
       </c>
       <c r="C22" s="3"/>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -686,7 +686,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -697,7 +697,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -708,7 +708,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -719,7 +719,7 @@
         <v>72.709999999999994</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -730,7 +730,7 @@
         <v>38.75</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>5</v>
       </c>
@@ -741,7 +741,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>3</v>
       </c>
@@ -752,7 +752,7 @@
         <v>89.6</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -763,7 +763,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -774,7 +774,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>3</v>
       </c>
@@ -785,7 +785,7 @@
         <v>91.34</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>4</v>
       </c>
@@ -796,7 +796,7 @@
         <v>40.5</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -807,7 +807,7 @@
         <v>58.08</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>3</v>
       </c>
@@ -818,7 +818,7 @@
         <v>93.38</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>4</v>
       </c>
@@ -829,7 +829,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -840,7 +840,7 @@
         <v>58.08</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>3</v>
       </c>
@@ -851,7 +851,7 @@
         <v>96.25</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>4</v>
       </c>
@@ -862,7 +862,7 @@
         <v>63.07</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>5</v>
       </c>
@@ -873,7 +873,7 @@
         <v>67.099999999999994</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>3</v>
       </c>
@@ -884,7 +884,7 @@
         <v>97.48</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>4</v>
       </c>
@@ -895,7 +895,7 @@
         <v>69.459999999999994</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>5</v>
       </c>
@@ -903,7 +903,7 @@
         <v>46300</v>
       </c>
       <c r="C43">
-        <v>74.73</v>
+        <v>71.73</v>
       </c>
     </row>
   </sheetData>

--- a/avanceSEGMA.xlsx
+++ b/avanceSEGMA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avitaconstructora-my.sharepoint.com/personal/aolivares_avita_cl/Documents/OT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="159" documentId="7_{30C0E4BA-C577-AA4F-9580-3F64A608DEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A94F71CC-4A71-44A2-BA0D-AB1150F48CF9}"/>
+  <xr:revisionPtr revIDLastSave="166" documentId="7_{30C0E4BA-C577-AA4F-9580-3F64A608DEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE7F6683-96D6-4D3C-B561-7ECF60D842C9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="6">
   <si>
     <t>partida</t>
   </si>
@@ -440,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9976E081-C2DF-2D4C-9457-A38B86FA81C8}">
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
@@ -906,6 +906,39 @@
         <v>71.73</v>
       </c>
     </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B44" s="1">
+        <v>46308</v>
+      </c>
+      <c r="C44">
+        <v>98.9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" s="1">
+        <v>46308</v>
+      </c>
+      <c r="C45">
+        <v>89.1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>5</v>
+      </c>
+      <c r="B46" s="1">
+        <v>46308</v>
+      </c>
+      <c r="C46">
+        <v>88.28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="14" scale="130" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
